--- a/Client/Configs/GameConfig/Datas/stage.xlsx
+++ b/Client/Configs/GameConfig/Datas/stage.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,31 @@
           <t>firstWaveIndex</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>levelMode</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>minEnemyLevel</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>maxEnemyLevel</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>baseLevelOffset</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>powerScale</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -489,78 +514,153 @@
           <t>int</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>##</t>
+          <t>##group</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Stage id.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Program key.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Display name.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Route key.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Loop mode.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>First wave index.</t>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>c,s</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>##group</t>
+          <t>##</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Stage id.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Program key.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Display name.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Route key.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Loop mode.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>First wave index.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Enemy level mode.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Minimum enemy level.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Maximum enemy level.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Base level offset.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Stage power scale.</t>
         </is>
       </c>
     </row>
@@ -589,6 +689,23 @@
         </is>
       </c>
       <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>PartyAverage</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>1</v>
       </c>
     </row>
